--- a/セリフ編集/その他セリフ/03-因縁・絆イベント.xlsx
+++ b/セリフ編集/その他セリフ/03-因縁・絆イベント.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I189"/>
+  <dimension ref="A1:I211"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -5216,7 +5216,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.normal._default[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal._default[1]</t>
+          <t xml:space="preserve">ahead.normal._default[1]</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="5">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="G157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わってないんだろうけど。……でも次も私が勝つよ</t>
+          <t xml:space="preserve">終わったはずなのに、まだ胃の底が重い</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal._default[2]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.normal._default[2]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal._default[2]</t>
+          <t xml:space="preserve">ahead.normal._default[2]</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="5">
@@ -5273,14 +5273,14 @@
       </c>
       <c r="G158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで終わり……というわけには行かないよね</t>
+          <t xml:space="preserve">もう一度勝てば消えるのかな。……多分、消えない</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.bold._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.bold._default[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold._default[1]</t>
+          <t xml:space="preserve">ahead.bold._default[1]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="6">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="G159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は私の勝ち。でも再戦はありそうね……</t>
+          <t xml:space="preserve">勝った側が、いつまで覚えてなきゃいけないの</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.quiet._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.bold._default[2]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5322,29 +5322,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">ahead.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（相手の方を一瞬だけ振り返る）</t>
+          <t xml:space="preserve">終わらせたのは私。付き合ってやるのは、これで最後</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.shy._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.quiet._default[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5354,29 +5354,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">ahead.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…よかった…でも、次も頑張らなきゃ…</t>
+          <t xml:space="preserve">………（終わったはずの相手を、じっと見ている）</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.easygoing._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.shy._default[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5386,29 +5386,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">ahead.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一個勝ち！ でもまだまだこれからだよ！</t>
+          <t xml:space="preserve">…もう終わったのに…どうして、また気になるんだろう…</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.earnest._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.easygoing._default[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5418,29 +5418,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">ahead.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無事勝ちました。でもこの因縁は、まだ続きそうね</t>
+          <t xml:space="preserve">はぁ……また？ もう終わった話でしょ、これ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.emotional._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.easygoing._default[2]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">ahead.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った……！ でもまだ……まだ終わらない……！</t>
+          <t xml:space="preserve">勝っても軽くならないもんだね。……不思議</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.earnest._default[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5482,29 +5482,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">ahead.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は負けない。絶対に</t>
+          <t xml:space="preserve">決着はつきました。……私の中だけ、まだです</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal._default[2]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.earnest._default[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5514,29 +5514,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">ahead.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……覚えてて。この借りは必ず返すから</t>
+          <t xml:space="preserve">勝った人間が引きずるのは、変な話ですね</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.bold._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.emotional._default[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5546,29 +5546,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">ahead.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この負けは認めない。必ず借りを返す</t>
+          <t xml:space="preserve">終わったって言っただろ……！ なんでまだ、いるんだ</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.quiet._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.normal._default[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5578,29 +5578,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">behind.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに拳を握りしめる）</t>
+          <t xml:space="preserve">終わったことにされた。私だけ、置いていかれたまま</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.shy._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.normal._default[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5610,29 +5610,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">behind.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けちゃった……悔しい…です……</t>
+          <t xml:space="preserve">忘れられたら楽だったのに。……よく覚えてるんだ、これが</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.easygoing._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.bold._default[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5642,29 +5642,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">behind.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちゃー、負けた。でも次があるさ。絶対やり返す！</t>
+          <t xml:space="preserve">終わりってことにされてる。でも私はまだ認めない</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.earnest._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.bold._default[2]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5674,29 +5674,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">behind.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。でも諦めません。必ず借りを返します</t>
+          <t xml:space="preserve">もう格付けは済んでいるのかも。それでも・・・</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.emotional._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.quiet._default[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">behind.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい……！ 絶対……絶対やり返す……！</t>
+          <t xml:space="preserve">………（あの日の敗北の瞬間が、まだ耳から抜けない）</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.shy._default[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5738,29 +5738,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">behind.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見たか！ 私が格下だなんて、もう言わせない……！</t>
+          <t xml:space="preserve">…あの日敗北した屈辱を…まだ、毎晩思い出すんです…</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.bold._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.easygoing._default[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5770,29 +5770,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">behind.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ついに……勝った……！ ずっと待ってた……！</t>
+          <t xml:space="preserve">みんな綺麗に忘れてるね。……あたしは忘れないけど</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.quiet._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.easygoing._default[2]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5802,29 +5802,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">behind.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（膝をつき、震えている）……勝った…？</t>
+          <t xml:space="preserve">いつまでやるんだろうね、これ。……やめられないけど</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.shy._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.earnest._default[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5834,29 +5834,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">behind.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…うそ…私が…？ ほんとに…？（膝から崩れる）</t>
+          <t xml:space="preserve">あの負けを、まだ一度も納得できていません</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.easygoing._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.earnest._default[2]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5866,29 +5866,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">behind.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっそ……勝っちゃった……！ やばい、信じられない……！</t>
+          <t xml:space="preserve">終わったと言われるたび、足元が抜けるんです</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.earnest._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.emotional._default[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5898,29 +5898,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest._default[1]</t>
+          <t xml:space="preserve">behind.emotional._default[1]</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="10">
         <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりました……！ ずっとこの人を目標にしてきて……ついに……！</t>
+          <t xml:space="preserve">終わってない……！ 勝手に終わらせるな……！</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal._default[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5930,29 +5930,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">winnerLines.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った……！ 勝ったよ……！ ずっと……ずっと追いかけてきたんだ……！（号泣）</t>
+          <t xml:space="preserve">まだ終わってないんだろうけど。……でも次も私が勝つよ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal._default[2]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal._default[1]</t>
+          <t xml:space="preserve">winnerLines.normal._default[2]</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="5">
@@ -5977,14 +5977,14 @@
       </c>
       <c r="G180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">噓でしょ？……こんなはずじゃ……</t>
+          <t xml:space="preserve">これで終わり……というわけには行かないよね</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal._default[2]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.bold._default[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5994,29 +5994,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">winnerLines.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんで……なんで負けたの……？</t>
+          <t xml:space="preserve">今日は私の勝ち。でも再戦はありそうね……</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.quiet._default[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6026,29 +6026,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">winnerLines.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めない……！ こんな結果……認めない……！</t>
+          <t xml:space="preserve">………（相手の方を一瞬だけ振り返る）</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold._default[2]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.shy._default[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6058,29 +6058,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">winnerLines.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありえない……嘘でしょ……！</t>
+          <t xml:space="preserve">勝てた…よかった…でも、次も頑張らなきゃ…</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.easygoing._default[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6090,29 +6090,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">winnerLines.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（呆然と天井を見上げている）</t>
+          <t xml:space="preserve">一個勝ち！ でもまだまだこれからだよ！</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.earnest._default[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6122,29 +6122,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">winnerLines.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…え……うそ…………（何が起きたかわかっていない）</t>
+          <t xml:space="preserve">無事勝ちました。でもこの因縁は、まだ続きそうね</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.emotional._default[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6154,29 +6154,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">winnerLines.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ……嘘でしょ……マジで……？</t>
+          <t xml:space="preserve">勝った……！ でもまだ……まだ終わらない……！</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal._default[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6186,29 +6186,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">loserLines.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなはずでは……油断したつもりはなかったのに……</t>
+          <t xml:space="preserve">次は負けない。絶対に</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest._default[2]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal._default[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6218,59 +6218,763 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">loserLines.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じられません……なぜ……</t>
+          <t xml:space="preserve">……覚えてて。この借りは必ず返すから</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この負けは認めない。必ず借りを返す</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（静かに拳を握りしめる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…負けちゃった……悔しい…です……</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あちゃー、負けた。でも次があるさ。絶対やり返す！</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けました。でも諦めません。必ず借りを返します</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">悔しい……！ 絶対……絶対やり返す……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winnerLines.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見たか！ 私が格下だなんて、もう言わせない……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winnerLines.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ついに……勝った……！ ずっと待ってた……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winnerLines.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（膝をつき、震えている）……勝った…？</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="40" customHeight="1">
+      <c r="A198" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winnerLines.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">え…うそ…私が…？ ほんとに…？（膝から崩れる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winnerLines.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うっそ……勝っちゃった……！ やばい、信じられない……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winnerLines.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やりました……！ ずっとこの人を目標にしてきて……ついに……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winnerLines.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝った……！ 勝ったよ……！ ずっと……ずっと追いかけてきたんだ……！（号泣）</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">噓でしょ？……こんなはずじゃ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">なんで……なんで負けたの……？</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">認めない……！ こんな結果……認めない……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありえない……嘘でしょ……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（呆然と天井を見上げている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…え……うそ…………（何が起きたかわかっていない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">えっ……嘘でしょ……マジで……？</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こんなはずでは……油断したつもりはなかったのに……</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loserLines.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">信じられません……なぜ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.emotional._default[1]</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr" s="2">
+      <c r="B211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr" s="12">
+      <c r="D211" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">loserLines.emotional._default[1]</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr" s="10">
+      <c r="F211" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">感情的</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr" s="3">
+      <c r="G211" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">嫌だ……！ こんなの嫌だ……！ なんで……！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I189"/>
+  <autoFilter ref="A1:I211"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/その他セリフ/03-因縁・絆イベント.xlsx
+++ b/セリフ編集/その他セリフ/03-因縁・絆イベント.xlsx
@@ -256,7 +256,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker._default.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -271,7 +271,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal._default[1]</t>
+          <t xml:space="preserve">attacker._default.normal[1]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="5">
@@ -288,7 +288,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker._default.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -303,7 +303,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal._default[2]</t>
+          <t xml:space="preserve">attacker._default.normal[2]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="5">
@@ -320,7 +320,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal._default[3]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker._default.normal[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal._default[3]</t>
+          <t xml:space="preserve">attacker._default.normal[3]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="5">
@@ -352,7 +352,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker._default.bold[1]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -367,7 +367,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold._default[1]</t>
+          <t xml:space="preserve">attacker._default.bold[1]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="6">
@@ -384,7 +384,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.bold._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker._default.bold[2]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -399,7 +399,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold._default[2]</t>
+          <t xml:space="preserve">attacker._default.bold[2]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="6">
@@ -416,7 +416,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker._default.quiet[1]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -431,7 +431,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet._default[1]</t>
+          <t xml:space="preserve">attacker._default.quiet[1]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="7">
@@ -448,7 +448,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker._default.shy[1]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -463,7 +463,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.shy._default[1]</t>
+          <t xml:space="preserve">attacker._default.shy[1]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="8">
@@ -480,7 +480,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -495,7 +495,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing._default[1]</t>
+          <t xml:space="preserve">attacker._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="9">
@@ -512,7 +512,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.easygoing._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -527,7 +527,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing._default[2]</t>
+          <t xml:space="preserve">attacker._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="9">
@@ -544,7 +544,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker._default.earnest[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -559,7 +559,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest._default[1]</t>
+          <t xml:space="preserve">attacker._default.earnest[1]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="10">
@@ -576,7 +576,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.earnest._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker._default.earnest[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -591,7 +591,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest._default[2]</t>
+          <t xml:space="preserve">attacker._default.earnest[2]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="10">
@@ -608,7 +608,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker._default.emotional[1]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -623,7 +623,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.emotional._default[1]</t>
+          <t xml:space="preserve">attacker._default.emotional[1]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="10">
@@ -640,7 +640,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender._default.normal[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal._default[1]</t>
+          <t xml:space="preserve">defender._default.normal[1]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="5">
@@ -672,7 +672,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender._default.normal[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -687,7 +687,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal._default[2]</t>
+          <t xml:space="preserve">defender._default.normal[2]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="5">
@@ -704,7 +704,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal._default[3]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender._default.normal[3]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal._default[3]</t>
+          <t xml:space="preserve">defender._default.normal[3]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="5">
@@ -736,7 +736,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender._default.bold[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold._default[1]</t>
+          <t xml:space="preserve">defender._default.bold[1]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="6">
@@ -768,7 +768,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.bold._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender._default.bold[2]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold._default[2]</t>
+          <t xml:space="preserve">defender._default.bold[2]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="6">
@@ -800,7 +800,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender._default.quiet[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -815,7 +815,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet._default[1]</t>
+          <t xml:space="preserve">defender._default.quiet[1]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="7">
@@ -832,7 +832,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender._default.shy[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.shy._default[1]</t>
+          <t xml:space="preserve">defender._default.shy[1]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="8">
@@ -864,7 +864,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -879,7 +879,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing._default[1]</t>
+          <t xml:space="preserve">defender._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="9">
@@ -896,7 +896,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender._default.earnest[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest._default[1]</t>
+          <t xml:space="preserve">defender._default.earnest[1]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="10">
@@ -928,7 +928,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.earnest._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender._default.earnest[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -943,7 +943,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest._default[2]</t>
+          <t xml:space="preserve">defender._default.earnest[2]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="10">
@@ -960,7 +960,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender._default.emotional[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -975,7 +975,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.emotional._default[1]</t>
+          <t xml:space="preserve">defender._default.emotional[1]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="10">
@@ -992,7 +992,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker._default.normal[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.normal._default[1]</t>
+          <t xml:space="preserve">fateAttacker._default.normal[1]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="5">
@@ -1024,7 +1024,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker._default.normal[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.normal._default[2]</t>
+          <t xml:space="preserve">fateAttacker._default.normal[2]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="5">
@@ -1056,7 +1056,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker._default.bold[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.bold._default[1]</t>
+          <t xml:space="preserve">fateAttacker._default.bold[1]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="6">
@@ -1088,7 +1088,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.bold._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker._default.bold[2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.bold._default[2]</t>
+          <t xml:space="preserve">fateAttacker._default.bold[2]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="6">
@@ -1120,7 +1120,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker._default.quiet[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.quiet._default[1]</t>
+          <t xml:space="preserve">fateAttacker._default.quiet[1]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="7">
@@ -1152,7 +1152,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker._default.shy[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.shy._default[1]</t>
+          <t xml:space="preserve">fateAttacker._default.shy[1]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="8">
@@ -1184,7 +1184,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.easygoing._default[1]</t>
+          <t xml:space="preserve">fateAttacker._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="9">
@@ -1216,7 +1216,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker._default.earnest[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.earnest._default[1]</t>
+          <t xml:space="preserve">fateAttacker._default.earnest[1]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="10">
@@ -1248,7 +1248,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker._default.emotional[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.emotional._default[1]</t>
+          <t xml:space="preserve">fateAttacker._default.emotional[1]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="10">
@@ -1280,7 +1280,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender._default.normal[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.normal._default[1]</t>
+          <t xml:space="preserve">fateDefender._default.normal[1]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="5">
@@ -1312,7 +1312,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender._default.normal[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.normal._default[2]</t>
+          <t xml:space="preserve">fateDefender._default.normal[2]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="5">
@@ -1344,7 +1344,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender._default.bold[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.bold._default[1]</t>
+          <t xml:space="preserve">fateDefender._default.bold[1]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="6">
@@ -1376,7 +1376,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.bold._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender._default.bold[2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.bold._default[2]</t>
+          <t xml:space="preserve">fateDefender._default.bold[2]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="6">
@@ -1408,7 +1408,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender._default.quiet[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.quiet._default[1]</t>
+          <t xml:space="preserve">fateDefender._default.quiet[1]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="7">
@@ -1440,7 +1440,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender._default.shy[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.shy._default[1]</t>
+          <t xml:space="preserve">fateDefender._default.shy[1]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="8">
@@ -1472,7 +1472,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.easygoing._default[1]</t>
+          <t xml:space="preserve">fateDefender._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="9">
@@ -1504,7 +1504,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender._default.earnest[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.earnest._default[1]</t>
+          <t xml:space="preserve">fateDefender._default.earnest[1]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="10">
@@ -1536,7 +1536,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender._default.emotional[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.emotional._default[1]</t>
+          <t xml:space="preserve">fateDefender._default.emotional[1]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="10">
@@ -1568,7 +1568,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker._default.normal[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal._default[1]</t>
+          <t xml:space="preserve">attacker._default.normal[1]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="5">
@@ -1600,7 +1600,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker._default.normal[2]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal._default[2]</t>
+          <t xml:space="preserve">attacker._default.normal[2]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="5">
@@ -1632,7 +1632,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal._default[3]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker._default.normal[3]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal._default[3]</t>
+          <t xml:space="preserve">attacker._default.normal[3]</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="5">
@@ -1664,7 +1664,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker._default.bold[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold._default[1]</t>
+          <t xml:space="preserve">attacker._default.bold[1]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="6">
@@ -1696,7 +1696,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.bold._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker._default.bold[2]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold._default[2]</t>
+          <t xml:space="preserve">attacker._default.bold[2]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="6">
@@ -1728,7 +1728,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker._default.quiet[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet._default[1]</t>
+          <t xml:space="preserve">attacker._default.quiet[1]</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="7">
@@ -1760,7 +1760,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker._default.shy[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.shy._default[1]</t>
+          <t xml:space="preserve">attacker._default.shy[1]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="8">
@@ -1792,7 +1792,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing._default[1]</t>
+          <t xml:space="preserve">attacker._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="9">
@@ -1824,7 +1824,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker._default.earnest[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest._default[1]</t>
+          <t xml:space="preserve">attacker._default.earnest[1]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="10">
@@ -1856,7 +1856,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.earnest._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker._default.earnest[2]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest._default[2]</t>
+          <t xml:space="preserve">attacker._default.earnest[2]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="10">
@@ -1888,7 +1888,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker._default.emotional[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.emotional._default[1]</t>
+          <t xml:space="preserve">attacker._default.emotional[1]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="10">
@@ -1920,7 +1920,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender._default.normal[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal._default[1]</t>
+          <t xml:space="preserve">defender._default.normal[1]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="5">
@@ -1952,7 +1952,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender._default.normal[2]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal._default[2]</t>
+          <t xml:space="preserve">defender._default.normal[2]</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="5">
@@ -1984,7 +1984,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal._default[3]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender._default.normal[3]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal._default[3]</t>
+          <t xml:space="preserve">defender._default.normal[3]</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="5">
@@ -2016,7 +2016,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender._default.bold[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold._default[1]</t>
+          <t xml:space="preserve">defender._default.bold[1]</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="6">
@@ -2048,7 +2048,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.bold._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender._default.bold[2]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold._default[2]</t>
+          <t xml:space="preserve">defender._default.bold[2]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="6">
@@ -2080,7 +2080,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender._default.quiet[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet._default[1]</t>
+          <t xml:space="preserve">defender._default.quiet[1]</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="7">
@@ -2112,7 +2112,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender._default.shy[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.shy._default[1]</t>
+          <t xml:space="preserve">defender._default.shy[1]</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="8">
@@ -2144,7 +2144,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing._default[1]</t>
+          <t xml:space="preserve">defender._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="9">
@@ -2176,7 +2176,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender._default.earnest[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest._default[1]</t>
+          <t xml:space="preserve">defender._default.earnest[1]</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="10">
@@ -2208,7 +2208,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender._default.emotional[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.emotional._default[1]</t>
+          <t xml:space="preserve">defender._default.emotional[1]</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="10">
@@ -2240,7 +2240,7 @@
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker._default.normal[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal._default[1]</t>
+          <t xml:space="preserve">attacker._default.normal[1]</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="5">
@@ -2272,7 +2272,7 @@
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker._default.normal[2]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal._default[2]</t>
+          <t xml:space="preserve">attacker._default.normal[2]</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="5">
@@ -2304,7 +2304,7 @@
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker._default.bold[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold._default[1]</t>
+          <t xml:space="preserve">attacker._default.bold[1]</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="6">
@@ -2336,7 +2336,7 @@
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.bold._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker._default.bold[2]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold._default[2]</t>
+          <t xml:space="preserve">attacker._default.bold[2]</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="6">
@@ -2368,7 +2368,7 @@
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker._default.quiet[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet._default[1]</t>
+          <t xml:space="preserve">attacker._default.quiet[1]</t>
         </is>
       </c>
       <c r="F68" t="inlineStr" s="7">
@@ -2400,7 +2400,7 @@
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker._default.shy[1]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.shy._default[1]</t>
+          <t xml:space="preserve">attacker._default.shy[1]</t>
         </is>
       </c>
       <c r="F69" t="inlineStr" s="8">
@@ -2432,7 +2432,7 @@
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing._default[1]</t>
+          <t xml:space="preserve">attacker._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F70" t="inlineStr" s="9">
@@ -2464,7 +2464,7 @@
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker._default.earnest[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest._default[1]</t>
+          <t xml:space="preserve">attacker._default.earnest[1]</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="10">
@@ -2496,7 +2496,7 @@
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker._default.emotional[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.emotional._default[1]</t>
+          <t xml:space="preserve">attacker._default.emotional[1]</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="10">
@@ -2528,7 +2528,7 @@
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender._default.normal[1]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal._default[1]</t>
+          <t xml:space="preserve">defender._default.normal[1]</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="5">
@@ -2560,7 +2560,7 @@
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender._default.normal[2]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal._default[2]</t>
+          <t xml:space="preserve">defender._default.normal[2]</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="5">
@@ -2592,7 +2592,7 @@
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender._default.bold[1]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold._default[1]</t>
+          <t xml:space="preserve">defender._default.bold[1]</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="6">
@@ -2624,7 +2624,7 @@
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.bold._default[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender._default.bold[2]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold._default[2]</t>
+          <t xml:space="preserve">defender._default.bold[2]</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="6">
@@ -2656,7 +2656,7 @@
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender._default.quiet[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet._default[1]</t>
+          <t xml:space="preserve">defender._default.quiet[1]</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="7">
@@ -2688,7 +2688,7 @@
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender._default.shy[1]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.shy._default[1]</t>
+          <t xml:space="preserve">defender._default.shy[1]</t>
         </is>
       </c>
       <c r="F78" t="inlineStr" s="8">
@@ -2720,7 +2720,7 @@
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing._default[1]</t>
+          <t xml:space="preserve">defender._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F79" t="inlineStr" s="9">
@@ -2752,7 +2752,7 @@
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender._default.earnest[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest._default[1]</t>
+          <t xml:space="preserve">defender._default.earnest[1]</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="10">
@@ -2784,7 +2784,7 @@
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender._default.emotional[1]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.emotional._default[1]</t>
+          <t xml:space="preserve">defender._default.emotional[1]</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="10">
@@ -2816,7 +2816,7 @@
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner._default.normal[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal._default[1]</t>
+          <t xml:space="preserve">winner._default.normal[1]</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="5">
@@ -2848,7 +2848,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal._default[2]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner._default.normal[2]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal._default[2]</t>
+          <t xml:space="preserve">winner._default.normal[2]</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="5">
@@ -2880,7 +2880,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner._default.bold[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold._default[1]</t>
+          <t xml:space="preserve">winner._default.bold[1]</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="6">
@@ -2912,7 +2912,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.bold._default[2]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner._default.bold[2]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold._default[2]</t>
+          <t xml:space="preserve">winner._default.bold[2]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="6">
@@ -2944,7 +2944,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner._default.quiet[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet._default[1]</t>
+          <t xml:space="preserve">winner._default.quiet[1]</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="7">
@@ -2976,7 +2976,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner._default.shy[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.shy._default[1]</t>
+          <t xml:space="preserve">winner._default.shy[1]</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="8">
@@ -3008,7 +3008,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing._default[1]</t>
+          <t xml:space="preserve">winner._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="9">
@@ -3040,7 +3040,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner._default.earnest[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest._default[1]</t>
+          <t xml:space="preserve">winner._default.earnest[1]</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="10">
@@ -3072,7 +3072,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.earnest._default[2]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner._default.earnest[2]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest._default[2]</t>
+          <t xml:space="preserve">winner._default.earnest[2]</t>
         </is>
       </c>
       <c r="F90" t="inlineStr" s="10">
@@ -3104,7 +3104,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner._default.emotional[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional._default[1]</t>
+          <t xml:space="preserve">winner._default.emotional[1]</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="10">
@@ -3136,7 +3136,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser._default.normal[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal._default[1]</t>
+          <t xml:space="preserve">loser._default.normal[1]</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="5">
@@ -3168,7 +3168,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal._default[2]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser._default.normal[2]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal._default[2]</t>
+          <t xml:space="preserve">loser._default.normal[2]</t>
         </is>
       </c>
       <c r="F93" t="inlineStr" s="5">
@@ -3200,7 +3200,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser._default.bold[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold._default[1]</t>
+          <t xml:space="preserve">loser._default.bold[1]</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="6">
@@ -3232,7 +3232,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.bold._default[2]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser._default.bold[2]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold._default[2]</t>
+          <t xml:space="preserve">loser._default.bold[2]</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="6">
@@ -3264,7 +3264,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser._default.quiet[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet._default[1]</t>
+          <t xml:space="preserve">loser._default.quiet[1]</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="7">
@@ -3296,7 +3296,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser._default.shy[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.shy._default[1]</t>
+          <t xml:space="preserve">loser._default.shy[1]</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="8">
@@ -3328,7 +3328,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing._default[1]</t>
+          <t xml:space="preserve">loser._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="9">
@@ -3360,7 +3360,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser._default.earnest[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest._default[1]</t>
+          <t xml:space="preserve">loser._default.earnest[1]</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="10">
@@ -3392,7 +3392,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.earnest._default[2]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser._default.earnest[2]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest._default[2]</t>
+          <t xml:space="preserve">loser._default.earnest[2]</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="10">
@@ -3424,7 +3424,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser._default.emotional[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional._default[1]</t>
+          <t xml:space="preserve">loser._default.emotional[1]</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="10">
@@ -3456,7 +3456,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner._default.normal[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.normal._default[1]</t>
+          <t xml:space="preserve">fateWinner._default.normal[1]</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="5">
@@ -3488,7 +3488,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner._default.bold[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.bold._default[1]</t>
+          <t xml:space="preserve">fateWinner._default.bold[1]</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="6">
@@ -3520,7 +3520,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.bold._default[2]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner._default.bold[2]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.bold._default[2]</t>
+          <t xml:space="preserve">fateWinner._default.bold[2]</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="6">
@@ -3552,7 +3552,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner._default.quiet[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.quiet._default[1]</t>
+          <t xml:space="preserve">fateWinner._default.quiet[1]</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="7">
@@ -3584,7 +3584,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner._default.shy[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.shy._default[1]</t>
+          <t xml:space="preserve">fateWinner._default.shy[1]</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="8">
@@ -3616,7 +3616,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.easygoing._default[1]</t>
+          <t xml:space="preserve">fateWinner._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="9">
@@ -3648,7 +3648,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner._default.earnest[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.earnest._default[1]</t>
+          <t xml:space="preserve">fateWinner._default.earnest[1]</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="10">
@@ -3680,7 +3680,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner._default.emotional[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.emotional._default[1]</t>
+          <t xml:space="preserve">fateWinner._default.emotional[1]</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="10">
@@ -3712,7 +3712,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser._default.normal[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.normal._default[1]</t>
+          <t xml:space="preserve">fateLoser._default.normal[1]</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="5">
@@ -3744,7 +3744,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser._default.bold[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.bold._default[1]</t>
+          <t xml:space="preserve">fateLoser._default.bold[1]</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="6">
@@ -3776,7 +3776,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.bold._default[2]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser._default.bold[2]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.bold._default[2]</t>
+          <t xml:space="preserve">fateLoser._default.bold[2]</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="6">
@@ -3808,7 +3808,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser._default.quiet[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.quiet._default[1]</t>
+          <t xml:space="preserve">fateLoser._default.quiet[1]</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="7">
@@ -3840,7 +3840,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser._default.shy[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.shy._default[1]</t>
+          <t xml:space="preserve">fateLoser._default.shy[1]</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="8">
@@ -3872,7 +3872,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.easygoing._default[1]</t>
+          <t xml:space="preserve">fateLoser._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="9">
@@ -3904,7 +3904,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser._default.earnest[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.earnest._default[1]</t>
+          <t xml:space="preserve">fateLoser._default.earnest[1]</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="10">
@@ -3936,7 +3936,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser._default.emotional[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.emotional._default[1]</t>
+          <t xml:space="preserve">fateLoser._default.emotional[1]</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="10">
@@ -3968,7 +3968,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner._default.normal[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal._default[1]</t>
+          <t xml:space="preserve">winner._default.normal[1]</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="5">
@@ -4000,7 +4000,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal._default[2]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner._default.normal[2]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal._default[2]</t>
+          <t xml:space="preserve">winner._default.normal[2]</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="5">
@@ -4032,7 +4032,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.bold._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner._default.bold[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold._default[1]</t>
+          <t xml:space="preserve">winner._default.bold[1]</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="6">
@@ -4064,7 +4064,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.bold._default[2]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner._default.bold[2]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold._default[2]</t>
+          <t xml:space="preserve">winner._default.bold[2]</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="6">
@@ -4096,7 +4096,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.quiet._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner._default.quiet[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet._default[1]</t>
+          <t xml:space="preserve">winner._default.quiet[1]</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="7">
@@ -4128,7 +4128,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.shy._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner._default.shy[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.shy._default[1]</t>
+          <t xml:space="preserve">winner._default.shy[1]</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="8">
@@ -4160,7 +4160,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.easygoing._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing._default[1]</t>
+          <t xml:space="preserve">winner._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="9">
@@ -4192,7 +4192,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.earnest._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner._default.earnest[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest._default[1]</t>
+          <t xml:space="preserve">winner._default.earnest[1]</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="10">
@@ -4224,7 +4224,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.earnest._default[2]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner._default.earnest[2]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest._default[2]</t>
+          <t xml:space="preserve">winner._default.earnest[2]</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="10">
@@ -4256,7 +4256,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.emotional._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner._default.emotional[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional._default[1]</t>
+          <t xml:space="preserve">winner._default.emotional[1]</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="10">
@@ -4288,7 +4288,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.normal._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser._default.normal[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal._default[1]</t>
+          <t xml:space="preserve">loser._default.normal[1]</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="5">
@@ -4320,7 +4320,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.normal._default[2]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser._default.normal[2]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal._default[2]</t>
+          <t xml:space="preserve">loser._default.normal[2]</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="5">
@@ -4352,7 +4352,7 @@
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.bold._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser._default.bold[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold._default[1]</t>
+          <t xml:space="preserve">loser._default.bold[1]</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="6">
@@ -4384,7 +4384,7 @@
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.bold._default[2]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser._default.bold[2]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold._default[2]</t>
+          <t xml:space="preserve">loser._default.bold[2]</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="6">
@@ -4416,7 +4416,7 @@
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.quiet._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser._default.quiet[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet._default[1]</t>
+          <t xml:space="preserve">loser._default.quiet[1]</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="7">
@@ -4448,7 +4448,7 @@
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.shy._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser._default.shy[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.shy._default[1]</t>
+          <t xml:space="preserve">loser._default.shy[1]</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="8">
@@ -4480,7 +4480,7 @@
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.easygoing._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing._default[1]</t>
+          <t xml:space="preserve">loser._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="9">
@@ -4512,7 +4512,7 @@
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.earnest._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser._default.earnest[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest._default[1]</t>
+          <t xml:space="preserve">loser._default.earnest[1]</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="10">
@@ -4544,7 +4544,7 @@
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.earnest._default[2]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser._default.earnest[2]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest._default[2]</t>
+          <t xml:space="preserve">loser._default.earnest[2]</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="10">
@@ -4576,7 +4576,7 @@
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.emotional._default[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser._default.emotional[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional._default[1]</t>
+          <t xml:space="preserve">loser._default.emotional[1]</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="10">
@@ -4608,7 +4608,7 @@
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner._default.normal[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal._default[1]</t>
+          <t xml:space="preserve">winner._default.normal[1]</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="5">
@@ -4640,7 +4640,7 @@
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal._default[2]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner._default.normal[2]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal._default[2]</t>
+          <t xml:space="preserve">winner._default.normal[2]</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="5">
@@ -4672,7 +4672,7 @@
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.bold._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner._default.bold[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold._default[1]</t>
+          <t xml:space="preserve">winner._default.bold[1]</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="6">
@@ -4704,7 +4704,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.bold._default[2]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner._default.bold[2]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold._default[2]</t>
+          <t xml:space="preserve">winner._default.bold[2]</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="6">
@@ -4736,7 +4736,7 @@
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.quiet._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner._default.quiet[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet._default[1]</t>
+          <t xml:space="preserve">winner._default.quiet[1]</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="7">
@@ -4768,7 +4768,7 @@
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.shy._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner._default.shy[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.shy._default[1]</t>
+          <t xml:space="preserve">winner._default.shy[1]</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="8">
@@ -4800,7 +4800,7 @@
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.easygoing._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing._default[1]</t>
+          <t xml:space="preserve">winner._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="9">
@@ -4832,7 +4832,7 @@
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.earnest._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner._default.earnest[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest._default[1]</t>
+          <t xml:space="preserve">winner._default.earnest[1]</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="10">
@@ -4864,7 +4864,7 @@
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.emotional._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner._default.emotional[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional._default[1]</t>
+          <t xml:space="preserve">winner._default.emotional[1]</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="10">
@@ -4896,7 +4896,7 @@
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser._default.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal._default[1]</t>
+          <t xml:space="preserve">loser._default.normal[1]</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="5">
@@ -4928,7 +4928,7 @@
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal._default[2]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser._default.normal[2]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal._default[2]</t>
+          <t xml:space="preserve">loser._default.normal[2]</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="5">
@@ -4960,7 +4960,7 @@
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.bold._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser._default.bold[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold._default[1]</t>
+          <t xml:space="preserve">loser._default.bold[1]</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="6">
@@ -4992,7 +4992,7 @@
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.bold._default[2]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser._default.bold[2]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold._default[2]</t>
+          <t xml:space="preserve">loser._default.bold[2]</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="6">
@@ -5024,7 +5024,7 @@
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.quiet._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser._default.quiet[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet._default[1]</t>
+          <t xml:space="preserve">loser._default.quiet[1]</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="7">
@@ -5056,7 +5056,7 @@
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.shy._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser._default.shy[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.shy._default[1]</t>
+          <t xml:space="preserve">loser._default.shy[1]</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="8">
@@ -5088,7 +5088,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.easygoing._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing._default[1]</t>
+          <t xml:space="preserve">loser._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="9">
@@ -5120,7 +5120,7 @@
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.earnest._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser._default.earnest[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest._default[1]</t>
+          <t xml:space="preserve">loser._default.earnest[1]</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="10">
@@ -5152,7 +5152,7 @@
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.earnest._default[2]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser._default.earnest[2]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest._default[2]</t>
+          <t xml:space="preserve">loser._default.earnest[2]</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="10">
@@ -5184,7 +5184,7 @@
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.emotional._default[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser._default.emotional[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional._default[1]</t>
+          <t xml:space="preserve">loser._default.emotional[1]</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="10">
@@ -5216,7 +5216,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.normal._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead._default.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.normal._default[1]</t>
+          <t xml:space="preserve">ahead._default.normal[1]</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="5">
@@ -5248,7 +5248,7 @@
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.normal._default[2]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead._default.normal[2]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.normal._default[2]</t>
+          <t xml:space="preserve">ahead._default.normal[2]</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="5">
@@ -5280,7 +5280,7 @@
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.bold._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead._default.bold[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.bold._default[1]</t>
+          <t xml:space="preserve">ahead._default.bold[1]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="6">
@@ -5312,7 +5312,7 @@
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.bold._default[2]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead._default.bold[2]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.bold._default[2]</t>
+          <t xml:space="preserve">ahead._default.bold[2]</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="6">
@@ -5344,7 +5344,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.quiet._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead._default.quiet[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.quiet._default[1]</t>
+          <t xml:space="preserve">ahead._default.quiet[1]</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="7">
@@ -5376,7 +5376,7 @@
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.shy._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead._default.shy[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.shy._default[1]</t>
+          <t xml:space="preserve">ahead._default.shy[1]</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="8">
@@ -5408,7 +5408,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.easygoing._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.easygoing._default[1]</t>
+          <t xml:space="preserve">ahead._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="9">
@@ -5440,7 +5440,7 @@
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.easygoing._default[2]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.easygoing._default[2]</t>
+          <t xml:space="preserve">ahead._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="9">
@@ -5472,7 +5472,7 @@
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.earnest._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead._default.earnest[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.earnest._default[1]</t>
+          <t xml:space="preserve">ahead._default.earnest[1]</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="10">
@@ -5504,7 +5504,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.earnest._default[2]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead._default.earnest[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.earnest._default[2]</t>
+          <t xml:space="preserve">ahead._default.earnest[2]</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="10">
@@ -5536,7 +5536,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.emotional._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead._default.emotional[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.emotional._default[1]</t>
+          <t xml:space="preserve">ahead._default.emotional[1]</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="10">
@@ -5568,7 +5568,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.normal._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind._default.normal[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.normal._default[1]</t>
+          <t xml:space="preserve">behind._default.normal[1]</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="5">
@@ -5600,7 +5600,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.normal._default[2]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind._default.normal[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.normal._default[2]</t>
+          <t xml:space="preserve">behind._default.normal[2]</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="5">
@@ -5632,7 +5632,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.bold._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind._default.bold[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.bold._default[1]</t>
+          <t xml:space="preserve">behind._default.bold[1]</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="6">
@@ -5664,7 +5664,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.bold._default[2]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind._default.bold[2]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.bold._default[2]</t>
+          <t xml:space="preserve">behind._default.bold[2]</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="6">
@@ -5696,7 +5696,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.quiet._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind._default.quiet[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.quiet._default[1]</t>
+          <t xml:space="preserve">behind._default.quiet[1]</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="7">
@@ -5728,7 +5728,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.shy._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind._default.shy[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.shy._default[1]</t>
+          <t xml:space="preserve">behind._default.shy[1]</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="8">
@@ -5760,7 +5760,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.easygoing._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.easygoing._default[1]</t>
+          <t xml:space="preserve">behind._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="9">
@@ -5792,7 +5792,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.easygoing._default[2]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.easygoing._default[2]</t>
+          <t xml:space="preserve">behind._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="9">
@@ -5824,7 +5824,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.earnest._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind._default.earnest[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.earnest._default[1]</t>
+          <t xml:space="preserve">behind._default.earnest[1]</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="10">
@@ -5856,7 +5856,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.earnest._default[2]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind._default.earnest[2]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.earnest._default[2]</t>
+          <t xml:space="preserve">behind._default.earnest[2]</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="10">
@@ -5888,7 +5888,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.emotional._default[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind._default.emotional[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.emotional._default[1]</t>
+          <t xml:space="preserve">behind._default.emotional[1]</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="10">
@@ -5920,7 +5920,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines._default.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.normal[1]</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="5">
@@ -5952,7 +5952,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal._default[2]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines._default.normal[2]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal._default[2]</t>
+          <t xml:space="preserve">winnerLines._default.normal[2]</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="5">
@@ -5984,7 +5984,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines._default.bold[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.bold[1]</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="6">
@@ -6016,7 +6016,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines._default.quiet[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.quiet[1]</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="7">
@@ -6048,7 +6048,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines._default.shy[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.shy._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.shy[1]</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="8">
@@ -6080,7 +6080,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="9">
@@ -6112,7 +6112,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines._default.earnest[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.earnest[1]</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="10">
@@ -6144,7 +6144,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines._default.emotional[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.emotional._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.emotional[1]</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="10">
@@ -6176,7 +6176,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines._default.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal._default[1]</t>
+          <t xml:space="preserve">loserLines._default.normal[1]</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="5">
@@ -6208,7 +6208,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal._default[2]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines._default.normal[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal._default[2]</t>
+          <t xml:space="preserve">loserLines._default.normal[2]</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="5">
@@ -6240,7 +6240,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.bold._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines._default.bold[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold._default[1]</t>
+          <t xml:space="preserve">loserLines._default.bold[1]</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="6">
@@ -6272,7 +6272,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.quiet._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines._default.quiet[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet._default[1]</t>
+          <t xml:space="preserve">loserLines._default.quiet[1]</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="7">
@@ -6304,7 +6304,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.shy._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines._default.shy[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.shy._default[1]</t>
+          <t xml:space="preserve">loserLines._default.shy[1]</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="8">
@@ -6336,7 +6336,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.easygoing._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing._default[1]</t>
+          <t xml:space="preserve">loserLines._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="9">
@@ -6368,7 +6368,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.earnest._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines._default.earnest[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest._default[1]</t>
+          <t xml:space="preserve">loserLines._default.earnest[1]</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="10">
@@ -6400,7 +6400,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.emotional._default[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines._default.emotional[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.emotional._default[1]</t>
+          <t xml:space="preserve">loserLines._default.emotional[1]</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="10">
@@ -6432,7 +6432,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines._default.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.normal[1]</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="5">
@@ -6464,7 +6464,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.bold._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines._default.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.bold[1]</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="6">
@@ -6496,7 +6496,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.quiet._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines._default.quiet[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.quiet[1]</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="7">
@@ -6528,7 +6528,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.shy._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines._default.shy[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.shy._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.shy[1]</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="8">
@@ -6560,7 +6560,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.easygoing._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="9">
@@ -6592,7 +6592,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.earnest._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines._default.earnest[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.earnest[1]</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="10">
@@ -6624,7 +6624,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.emotional._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines._default.emotional[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.emotional._default[1]</t>
+          <t xml:space="preserve">winnerLines._default.emotional[1]</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="10">
@@ -6656,7 +6656,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines._default.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal._default[1]</t>
+          <t xml:space="preserve">loserLines._default.normal[1]</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="5">
@@ -6688,7 +6688,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal._default[2]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines._default.normal[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal._default[2]</t>
+          <t xml:space="preserve">loserLines._default.normal[2]</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="5">
@@ -6720,7 +6720,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines._default.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold._default[1]</t>
+          <t xml:space="preserve">loserLines._default.bold[1]</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="6">
@@ -6752,7 +6752,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold._default[2]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines._default.bold[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold._default[2]</t>
+          <t xml:space="preserve">loserLines._default.bold[2]</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="6">
@@ -6784,7 +6784,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.quiet._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines._default.quiet[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet._default[1]</t>
+          <t xml:space="preserve">loserLines._default.quiet[1]</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="7">
@@ -6816,7 +6816,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.shy._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines._default.shy[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.shy._default[1]</t>
+          <t xml:space="preserve">loserLines._default.shy[1]</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="8">
@@ -6848,7 +6848,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.easygoing._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing._default[1]</t>
+          <t xml:space="preserve">loserLines._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="9">
@@ -6880,7 +6880,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines._default.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest._default[1]</t>
+          <t xml:space="preserve">loserLines._default.earnest[1]</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="10">
@@ -6912,7 +6912,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest._default[2]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines._default.earnest[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest._default[2]</t>
+          <t xml:space="preserve">loserLines._default.earnest[2]</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="10">
@@ -6944,7 +6944,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.emotional._default[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines._default.emotional[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.emotional._default[1]</t>
+          <t xml:space="preserve">loserLines._default.emotional[1]</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="10">
